--- a/OCT_2026/Target Lahore October-2026.xlsx
+++ b/OCT_2026/Target Lahore October-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78FA5E0-1DEA-4755-B541-1030C03833A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5831487-9FE4-47C0-BB59-AA51F71D67BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
